--- a/4P_Index_Loi_2019-12_CGCT.xlsx
+++ b/4P_Index_Loi_2019-12_CGCT.xlsx
@@ -601,13 +601,9 @@
         </is>
       </c>
       <c r="E2" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>Art. 195 bis(1): minimum CEL allocation not below FCFA 12,000,000 per commune per year.</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F2" s="2" t="inlineStr"/>
       <c r="G2" s="2" t="n">
         <v>1</v>
       </c>
@@ -698,13 +694,9 @@
         </is>
       </c>
       <c r="E3" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>Art. 195 bis(1): minimum CEL allocation not below FCFA 12,000,000 per commune per year.</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F3" s="2" t="inlineStr"/>
       <c r="G3" s="2" t="n">
         <v>1</v>
       </c>
@@ -795,13 +787,9 @@
         </is>
       </c>
       <c r="E4" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>Art. 195 bis(1): minimum CEL allocation not below FCFA 12,000,000 per commune per year.</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F4" s="2" t="inlineStr"/>
       <c r="G4" s="2" t="n">
         <v>1</v>
       </c>
